--- a/dataset_t6_grouped/results2/G4/G4_T1929_W0014F0002T0006Z000C1N56_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T1929_W0014F0002T0006Z000C1N56_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>52.24039594660411</v>
+        <v>8.489064341323168</v>
       </c>
       <c r="D2" t="n">
-        <v>48.5054689856764</v>
+        <v>7.882138710172415</v>
       </c>
       <c r="E2" t="n">
-        <v>11.80000217479012</v>
+        <v>1.917500353403395</v>
       </c>
       <c r="F2" t="n">
-        <v>11.46147422563019</v>
+        <v>1.862489561664905</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>44.8598836232303</v>
+        <v>7.289731088774923</v>
       </c>
       <c r="D3" t="n">
-        <v>42.36827894944543</v>
+        <v>6.884845329284883</v>
       </c>
       <c r="E3" t="n">
-        <v>11.80000217479012</v>
+        <v>1.917500353403395</v>
       </c>
       <c r="F3" t="n">
-        <v>11.46147422563019</v>
+        <v>1.862489561664905</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>54.9780989254601</v>
+        <v>8.933941075387267</v>
       </c>
       <c r="D4" t="n">
-        <v>51.34281445323652</v>
+        <v>8.343207348650935</v>
       </c>
       <c r="E4" t="n">
-        <v>11.80000217479012</v>
+        <v>1.917500353403395</v>
       </c>
       <c r="F4" t="n">
-        <v>11.46147422563019</v>
+        <v>1.862489561664905</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>36.18767499548861</v>
+        <v>5.8804971867669</v>
       </c>
       <c r="D5" t="n">
-        <v>32.56963615241538</v>
+        <v>5.2925658747675</v>
       </c>
       <c r="E5" t="n">
-        <v>11.80000217479012</v>
+        <v>1.917500353403395</v>
       </c>
       <c r="F5" t="n">
-        <v>11.46147422563019</v>
+        <v>1.862489561664905</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>20.96092838411127</v>
+        <v>3.406150862418081</v>
       </c>
       <c r="D6" t="n">
-        <v>19.77952506505492</v>
+        <v>3.214172823071424</v>
       </c>
       <c r="E6" t="n">
-        <v>11.80000217479012</v>
+        <v>1.917500353403395</v>
       </c>
       <c r="F6" t="n">
-        <v>11.46147422563019</v>
+        <v>1.862489561664905</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>62.62686346112439</v>
+        <v>10.17686531243271</v>
       </c>
       <c r="D7" t="n">
-        <v>60.046819869083</v>
+        <v>9.757608228725987</v>
       </c>
       <c r="E7" t="n">
-        <v>11.80000217479012</v>
+        <v>1.917500353403395</v>
       </c>
       <c r="F7" t="n">
-        <v>11.46147422563019</v>
+        <v>1.862489561664905</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>40.41200073075905</v>
+        <v>6.566950118748346</v>
       </c>
       <c r="D8" t="n">
-        <v>38.06223699815092</v>
+        <v>6.185113512199525</v>
       </c>
       <c r="E8" t="n">
-        <v>11.80000217479012</v>
+        <v>1.917500353403395</v>
       </c>
       <c r="F8" t="n">
-        <v>11.46147422563019</v>
+        <v>1.862489561664905</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>56.06841274048355</v>
+        <v>9.111117070328577</v>
       </c>
       <c r="D9" t="n">
-        <v>53.91889176315119</v>
+        <v>8.761819911512069</v>
       </c>
       <c r="E9" t="n">
-        <v>11.80000217479012</v>
+        <v>1.917500353403395</v>
       </c>
       <c r="F9" t="n">
-        <v>11.46147422563019</v>
+        <v>1.862489561664905</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>45.8359160928481</v>
+        <v>7.448336365087817</v>
       </c>
       <c r="D10" t="n">
-        <v>44.17067093692029</v>
+        <v>7.177734027249547</v>
       </c>
       <c r="E10" t="n">
-        <v>11.80000217479012</v>
+        <v>1.917500353403395</v>
       </c>
       <c r="F10" t="n">
-        <v>11.46147422563019</v>
+        <v>1.862489561664905</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
